--- a/resultados/facturas_lubrisol(2).xlsx
+++ b/resultados/facturas_lubrisol(2).xlsx
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,26 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,168 +437,1134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FV</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>deliver_to_collect_from</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>postal_code</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Identificación</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Email vendedor</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ID vendedor</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Código producto</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>8560</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>8560</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>AMANDA REINA QUIÑONEZ</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>AMANDA REINA QUIÑONEZ</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CR 13 No. 23 - 76  BRR GIRARDOT, Bucaramanga, 00000</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>37816926</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ANGEL RAUL RINCON ROJAS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ANGEL RAUL RINCON ROJAS</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CR 27 8 17 P1 BRR RICAURTE, Bogotá</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>80369062</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35900</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>LUBSYNT BLK 1/4 Galon (1.0 x 30,168.07) = 35,900.0</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>80103010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CL 39 SUR 68 M 36, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>901278215</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>112800</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>EMULSOL 40 1 Gal. (1.0 x 94,789.92) = 112,800.0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>80102002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ACEROS Y LAMINAS S.A.S.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ACEROS Y LAMINAS S.A.S.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CR 69 G 31 23 SUR, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>901374408</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>94200</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>LUB HD 46 1 Gal. (1.0 x 79,159.66) = 94,200.0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>80102005</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ACOPLES Y MANGUERAS CASTILLO SAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ACOPLES Y MANGUERAS CASTILLO SAS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CR 68 L  39 SUR 11, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>900796406</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>99100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>SULFOMET C 1 Gal. (1.0 x 83,277.31) = 99,100.0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>80102003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>222222222222</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>112800</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>EMULSOL 40 1 Gal. (1.0 x 94,789.92) = 112,800.0</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>80102002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ALIANZA INDUSTRIAL DELTA SAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ALIANZA INDUSTRIAL DELTA SAS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CL 16 NO. 19 A 41, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>901997982</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>637900</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>LUBSYNT BLK 5 Gal. (1.0 x 536,050.42) = 637,900.0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>80101010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CARPATEZ GROUP SAS</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CARPATEZ GROUP SAS</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CRT PRINCIPAL PILES VDA PILES, Palmira, 763537</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>900300532</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>ID: 660</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>2407700</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>2407700</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>EMULSOL 40 Aceite soluble para mecanizado 1/5 Gal (19 litros) (3.0 x 424,117.65) = 1,514,100.01; SULFOMET C Aceite para corte y roscado 1/5 Gal (19 litros) (2.0 x 375,462.18) = 893,599.99</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>50101110; 50101091</t>
+      <c r="K8" s="2" t="n">
+        <v>637900</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>637900</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>LUBSYNT BLK Fluido sintético para mecanizado 1/5 Gal (19 litros) (1.0 x 536,050.42) = 637,900.0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>50101119</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8839</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8839</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>INGTROMOL SAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INGTROMOL SAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CL 37D SUR No 68L -76, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>800170414</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ID: 660</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>437400.01</v>
+      </c>
+      <c r="L9" t="n">
+        <v>437400.01</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>LUBGUIAS 2 Aceite para guías y bancadas 1/5 Gal (19 litros) (1.0 x 367,563.03) = 437,400.01</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50101159</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MECANIZADOS Y TROQUELADOS S.A.S.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MECANIZADOS Y TROQUELADOS S.A.S.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>CL 15 No 52 - 14, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>800233447</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>3170199.99</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>3170199.99</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>SULFOMET C Aceite para corte y roscado 1/5 Gal (19 litros) (2.0 x 375,462.18) = 893,599.99; LUBSYNT M22 Fluido sintético para mecanizado 1/5 Gal (19 litros) (2.0 x 956,554.62) = 2,276,600.0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>50101091; 50101113</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INDUSTRIAS FABRIMAQ S.A.S.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INDUSTRIAS FABRIMAQ S.A.S.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CR 64 A No. 5A - 43, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>900131184</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>637900</v>
+      </c>
+      <c r="L11" t="n">
+        <v>637900</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>LUBSYNT BLK Fluido sintético para mecanizado 1/5 Gal (19 litros) (1.0 x 536,050.42) = 637,900.0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>50101119</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL DE RACORES Y PARTES S.A.S INRAPARTES</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL DE RACORES Y PARTES S.A.S INRAPARTES</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CR 27 22 60 BRR SAMPER MENDOZA, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>800061262</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>437400.01</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>LUBGUIAS 2 Aceite para guías y bancadas 1/5 Gal (19 litros) (1.0 x 367,563.03) = 437,400.01</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>50101159</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VIMALUM S.A.S</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VIMALUM S.A.S</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CR 86 C BIS SUR 41 10, Bogotá, 110871</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>900110298</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>872198.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>872198.65</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SULFOMET C Aceite para corte y roscado 1/5 Gal (19 litros) (2.0 x 375,462.18) = 893,599.99</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>50101091</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>INDUMAG INGENIERIA SAS</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>INDUMAG INGENIERIA SAS</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CR 23 A 6 35, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>901045906</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>usuario pos</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>29300</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>EMULSOL 40 1/4 Gal. (1.0 x 24,621.85) = 29,300.0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>pvcarvajal@lubrisoldecolombia.com</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>522854991</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>80103002</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8834</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8834</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DIRIMPEX S.A.S</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIRIMPEX S.A.S</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CL 18 A No. 68 D - 80, Bogotá, 110931</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>860516281</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1138300</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1138300</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LUBSYNT M22 Fluido sintético para mecanizado 1/5 Gal (19 litros) (1.0 x 956,554.62) = 1,138,300.0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>50101113</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>8833</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>8833</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>COMPAÑIA COMUNITARIA METALMECANICA SAS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>COMPAÑIA COMUNITARIA METALMECANICA SAS</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>CR 32 No 38A - 45 SUR, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>800066320</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Gabino Porras Amaya</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1575700.01</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1575700.01</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>LUBGUIAS 2 Aceite para guías y bancadas 1/5 Gal (19 litros) (1.0 x 367,563.03) = 437,400.01; LUBSYNT M22 Fluido sintético para mecanizado 1/5 Gal (19 litros) (1.0 x 956,554.62) = 1,138,300.0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>andresgabinopor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1015460667</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>50101159; 50101113</t>
         </is>
       </c>
     </row>
